--- a/Data/EXCEL/Transfer/dividend/20260215_1_2/2065-dividend-20260215_1_2.xlsx
+++ b/Data/EXCEL/Transfer/dividend/20260215_1_2/2065-dividend-20260215_1_2.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Workspaces\xls2xlsx\transfer\dividend\20260215_1_2(所屬年度_現金殖利率＋股票殖利率)\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\workspaces\xls2xlxs\20260215_1_2\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{15C947A3-EAA6-49A8-982B-D23E0C68FE32}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{4BE1A387-63F9-4CFA-BAA9-67DB88B5362B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="9720" yWindow="2670" windowWidth="21285" windowHeight="16275" xr2:uid="{FA564D39-B9A7-4C3C-9CC6-1C4F08BB2985}"/>
+    <workbookView xWindow="3492" yWindow="1344" windowWidth="16656" windowHeight="10992" xr2:uid="{3A978EDD-F17A-450D-B1F9-D3A4455BC95A}"/>
   </bookViews>
   <sheets>
     <sheet name="2065-dividend-20260215_1_2" sheetId="1" r:id="rId1"/>
@@ -1493,26 +1493,26 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{54DB1481-88CF-4064-9EC6-9FC826428057}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9342B257-3F63-4F1F-A50A-5D8D8AD45588}">
   <dimension ref="A1:X47"/>
-  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="16.2" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="4.375" customWidth="1"/>
-    <col min="2" max="2" width="4.875" customWidth="1"/>
-    <col min="3" max="3" width="11" customWidth="1"/>
-    <col min="4" max="10" width="7.125" customWidth="1"/>
-    <col min="11" max="13" width="6.75" customWidth="1"/>
-    <col min="14" max="14" width="7.125" customWidth="1"/>
-    <col min="15" max="18" width="6.75" customWidth="1"/>
-    <col min="19" max="19" width="7.125" customWidth="1"/>
-    <col min="20" max="20" width="6.75" customWidth="1"/>
-    <col min="21" max="21" width="7.125" customWidth="1"/>
-    <col min="22" max="22" width="6.75" customWidth="1"/>
-    <col min="23" max="23" width="7.125" customWidth="1"/>
-    <col min="24" max="24" width="8.375" customWidth="1"/>
+    <col min="1" max="1" width="3.77734375" customWidth="1"/>
+    <col min="2" max="2" width="4.21875" customWidth="1"/>
+    <col min="3" max="3" width="9.6640625" customWidth="1"/>
+    <col min="4" max="10" width="6.109375" customWidth="1"/>
+    <col min="11" max="13" width="5.88671875" customWidth="1"/>
+    <col min="14" max="14" width="6.109375" customWidth="1"/>
+    <col min="15" max="18" width="5.88671875" customWidth="1"/>
+    <col min="19" max="19" width="6.109375" customWidth="1"/>
+    <col min="20" max="20" width="5.88671875" customWidth="1"/>
+    <col min="21" max="21" width="6.109375" customWidth="1"/>
+    <col min="22" max="22" width="5.88671875" customWidth="1"/>
+    <col min="23" max="23" width="6.109375" customWidth="1"/>
+    <col min="24" max="24" width="6.77734375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:24" s="1" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:24" s="1" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A1" s="19" t="s">
         <v>0</v>
       </c>
@@ -1546,7 +1546,7 @@
       <c r="W1" s="28"/>
       <c r="X1" s="20"/>
     </row>
-    <row r="2" spans="1:24" s="3" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:24" s="3" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A2" s="21" t="s">
         <v>1</v>
       </c>
@@ -1582,7 +1582,7 @@
       <c r="W2" s="30"/>
       <c r="X2" s="31"/>
     </row>
-    <row r="3" spans="1:24" s="3" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:24" s="3" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A3" s="21" t="s">
         <v>2</v>
       </c>
@@ -1634,7 +1634,7 @@
       </c>
       <c r="X3" s="34"/>
     </row>
-    <row r="4" spans="1:24" s="3" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:24" s="3" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A4" s="23"/>
       <c r="B4" s="24"/>
       <c r="C4" s="7"/>
@@ -1702,7 +1702,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="5" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A5" s="35">
         <v>2025</v>
       </c>
@@ -1774,7 +1774,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A6" s="11" t="s">
         <v>29</v>
       </c>
@@ -1848,7 +1848,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A7" s="11" t="s">
         <v>29</v>
       </c>
@@ -1922,7 +1922,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A8" s="11" t="s">
         <v>29</v>
       </c>
@@ -1996,7 +1996,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A9" s="11" t="s">
         <v>29</v>
       </c>
@@ -2070,7 +2070,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A10" s="37">
         <v>2024</v>
       </c>
@@ -2142,7 +2142,7 @@
         <v>10.3</v>
       </c>
     </row>
-    <row r="11" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A11" s="16" t="s">
         <v>29</v>
       </c>
@@ -2216,7 +2216,7 @@
         <v>9.19</v>
       </c>
     </row>
-    <row r="12" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A12" s="16" t="s">
         <v>29</v>
       </c>
@@ -2290,7 +2290,7 @@
         <v>1.07</v>
       </c>
     </row>
-    <row r="13" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A13" s="16" t="s">
         <v>29</v>
       </c>
@@ -2364,7 +2364,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A14" s="16" t="s">
         <v>29</v>
       </c>
@@ -2438,7 +2438,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A15" s="16" t="s">
         <v>29</v>
       </c>
@@ -2512,7 +2512,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="16" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A16" s="35">
         <v>2023</v>
       </c>
@@ -2584,7 +2584,7 @@
         <v>9.07</v>
       </c>
     </row>
-    <row r="17" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A17" s="11" t="s">
         <v>29</v>
       </c>
@@ -2658,7 +2658,7 @@
         <v>6.18</v>
       </c>
     </row>
-    <row r="18" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A18" s="11" t="s">
         <v>29</v>
       </c>
@@ -2732,7 +2732,7 @@
         <v>2.89</v>
       </c>
     </row>
-    <row r="19" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A19" s="11" t="s">
         <v>29</v>
       </c>
@@ -2806,7 +2806,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="20" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A20" s="11" t="s">
         <v>29</v>
       </c>
@@ -2880,7 +2880,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="21" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A21" s="11" t="s">
         <v>29</v>
       </c>
@@ -2954,7 +2954,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="22" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A22" s="37">
         <v>2022</v>
       </c>
@@ -3026,7 +3026,7 @@
         <v>11.3</v>
       </c>
     </row>
-    <row r="23" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A23" s="16" t="s">
         <v>29</v>
       </c>
@@ -3100,7 +3100,7 @@
         <v>7.79</v>
       </c>
     </row>
-    <row r="24" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A24" s="16" t="s">
         <v>29</v>
       </c>
@@ -3174,7 +3174,7 @@
         <v>3.53</v>
       </c>
     </row>
-    <row r="25" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A25" s="16" t="s">
         <v>29</v>
       </c>
@@ -3248,7 +3248,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="26" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A26" s="16" t="s">
         <v>29</v>
       </c>
@@ -3322,7 +3322,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="27" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A27" s="16" t="s">
         <v>29</v>
       </c>
@@ -3396,7 +3396,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="28" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A28" s="35">
         <v>2021</v>
       </c>
@@ -3468,7 +3468,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="29" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A29" s="11" t="s">
         <v>29</v>
       </c>
@@ -3542,7 +3542,7 @@
         <v>9.41</v>
       </c>
     </row>
-    <row r="30" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A30" s="11" t="s">
         <v>29</v>
       </c>
@@ -3616,7 +3616,7 @@
         <v>2.62</v>
       </c>
     </row>
-    <row r="31" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A31" s="11" t="s">
         <v>29</v>
       </c>
@@ -3690,7 +3690,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="32" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A32" s="11" t="s">
         <v>29</v>
       </c>
@@ -3764,7 +3764,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="33" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A33" s="37">
         <v>2020</v>
       </c>
@@ -3836,7 +3836,7 @@
         <v>6.9</v>
       </c>
     </row>
-    <row r="34" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A34" s="16" t="s">
         <v>29</v>
       </c>
@@ -3910,7 +3910,7 @@
         <v>4.51</v>
       </c>
     </row>
-    <row r="35" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A35" s="16" t="s">
         <v>29</v>
       </c>
@@ -3984,7 +3984,7 @@
         <v>2.39</v>
       </c>
     </row>
-    <row r="36" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A36" s="16" t="s">
         <v>29</v>
       </c>
@@ -4058,7 +4058,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="37" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A37" s="16" t="s">
         <v>29</v>
       </c>
@@ -4132,7 +4132,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="38" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A38" s="35">
         <v>2019</v>
       </c>
@@ -4204,7 +4204,7 @@
         <v>11.5</v>
       </c>
     </row>
-    <row r="39" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A39" s="37">
         <v>2018</v>
       </c>
@@ -4276,7 +4276,7 @@
         <v>9.44</v>
       </c>
     </row>
-    <row r="40" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A40" s="35">
         <v>2017</v>
       </c>
@@ -4348,7 +4348,7 @@
         <v>6.22</v>
       </c>
     </row>
-    <row r="41" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A41" s="37">
         <v>2016</v>
       </c>
@@ -4420,7 +4420,7 @@
         <v>7.69</v>
       </c>
     </row>
-    <row r="42" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A42" s="35">
         <v>2015</v>
       </c>
@@ -4492,7 +4492,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="43" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A43" s="37">
         <v>2014</v>
       </c>
@@ -4564,7 +4564,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="44" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A44" s="35">
         <v>2013</v>
       </c>
@@ -4636,7 +4636,7 @@
         <v>6.42</v>
       </c>
     </row>
-    <row r="45" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A45" s="37">
         <v>2012</v>
       </c>
@@ -4708,7 +4708,7 @@
         <v>5.44</v>
       </c>
     </row>
-    <row r="46" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A46" s="35">
         <v>2011</v>
       </c>
@@ -4780,7 +4780,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="47" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A47" s="37" t="s">
         <v>52</v>
       </c>
